--- a/tiflow-xborder/build/0.9.0/StructureDefinition-GEM-ERPEU-PR-PAR-AccessAuthorization-Request.xlsx
+++ b/tiflow-xborder/build/0.9.0/StructureDefinition-GEM-ERPEU-PR-PAR-AccessAuthorization-Request.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1294" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="230">
   <si>
     <t>Property</t>
   </si>
@@ -383,10 +383,6 @@
     <t>closed</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 inv-1:A parameter must have one and only one of (value, resource, part) {(part.exists() and value.empty() and resource.empty()) or (part.empty() and (value.exists() xor resource.exists()))}</t>
   </si>
@@ -427,6 +423,133 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user contentmodifiers</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
+    <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.name</t>
+  </si>
+  <si>
+    <t>Name from the definition</t>
+  </si>
+  <si>
+    <t>The name of the parameter (reference to the operation definition).</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.value[x]</t>
+  </si>
+  <si>
+    <t>base64Binary
+booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
+  </si>
+  <si>
+    <t>If parameter is a data type</t>
+  </si>
+  <si>
+    <t>If the parameter is a data type.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inv-1
+</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.resource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>If parameter is a whole resource</t>
+  </si>
+  <si>
+    <t>If the parameter is a whole resource.</t>
+  </si>
+  <si>
+    <t>When resolving references in resources, the operation definition may specify how references may be resolved between parameters. If a reference cannot be resolved between the parameters, the application should fall back to it's general resource resolution methods.</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.part</t>
+  </si>
+  <si>
+    <t>Named part of a multi-part parameter</t>
+  </si>
+  <si>
+    <t>A named part of a multi-part parameter.</t>
+  </si>
+  <si>
+    <t>Only one level of nested parameters is allowed.</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:countryCode</t>
+  </si>
+  <si>
+    <t>countryCode</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:countryCode.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:countryCode.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:countryCode.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:countryCode.name</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:countryCode.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/iso3166-1-2</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:countryCode.value[x].id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.value[x].id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:countryCode.value[x].extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.value[x].extension</t>
+  </si>
+  <si>
     <t xml:space="preserve">value:url}
 </t>
   </si>
@@ -435,143 +558,6 @@
   </si>
   <si>
     <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Parameters.parameter.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>BackboneElement.modifierExtension</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Parameters.parameter.name</t>
-  </si>
-  <si>
-    <t>Name from the definition</t>
-  </si>
-  <si>
-    <t>The name of the parameter (reference to the operation definition).</t>
-  </si>
-  <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
-    <t>Parameters.parameter.value[x]</t>
-  </si>
-  <si>
-    <t>base64Binary
-booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
-  </si>
-  <si>
-    <t>If parameter is a data type</t>
-  </si>
-  <si>
-    <t>If the parameter is a data type.</t>
-  </si>
-  <si>
-    <t>ele-1
-inv-1</t>
-  </si>
-  <si>
-    <t>Parameters.parameter.resource</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
-</t>
-  </si>
-  <si>
-    <t>If parameter is a whole resource</t>
-  </si>
-  <si>
-    <t>If the parameter is a whole resource.</t>
-  </si>
-  <si>
-    <t>When resolving references in resources, the operation definition may specify how references may be resolved between parameters. If a reference cannot be resolved between the parameters, the application should fall back to it's general resource resolution methods.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inv-1
-</t>
-  </si>
-  <si>
-    <t>Entity. Role, or Act</t>
-  </si>
-  <si>
-    <t>Parameters.parameter.part</t>
-  </si>
-  <si>
-    <t>Named part of a multi-part parameter</t>
-  </si>
-  <si>
-    <t>A named part of a multi-part parameter.</t>
-  </si>
-  <si>
-    <t>Only one level of nested parameters is allowed.</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:countryCode</t>
-  </si>
-  <si>
-    <t>countryCode</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:countryCode.id</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:countryCode.extension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:countryCode.modifierExtension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:countryCode.name</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:countryCode.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/iso3166-1-2</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:countryCode.value[x].id</t>
-  </si>
-  <si>
-    <t>Parameters.parameter.value[x].id</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:countryCode.value[x].extension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter.value[x].extension</t>
   </si>
   <si>
     <t>Parameters.parameter:countryCode.value[x].system</t>
@@ -1846,24 +1832,24 @@
         <v>77</v>
       </c>
       <c r="AI7" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="AJ7" t="s" s="2">
-        <v>120</v>
-      </c>
       <c r="AK7" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1886,13 +1872,13 @@
         <v>75</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1943,7 +1929,7 @@
         <v>75</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>76</v>
@@ -1966,14 +1952,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -1992,16 +1978,16 @@
         <v>75</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2039,19 +2025,19 @@
         <v>75</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>76</v>
@@ -2063,7 +2049,7 @@
         <v>75</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>75</v>
@@ -2074,14 +2060,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2100,19 +2086,19 @@
         <v>85</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>75</v>
@@ -2161,7 +2147,7 @@
         <v>75</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
@@ -2173,21 +2159,21 @@
         <v>75</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2210,17 +2196,15 @@
         <v>85</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>75</v>
@@ -2269,7 +2253,7 @@
         <v>75</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>84</v>
@@ -2292,10 +2276,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2318,13 +2302,13 @@
         <v>85</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2375,7 +2359,7 @@
         <v>75</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
@@ -2384,7 +2368,7 @@
         <v>84</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>96</v>
@@ -2393,15 +2377,15 @@
         <v>75</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2424,16 +2408,16 @@
         <v>85</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2483,7 +2467,7 @@
         <v>75</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -2492,7 +2476,7 @@
         <v>84</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>75</v>
@@ -2501,15 +2485,15 @@
         <v>75</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>159</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2535,13 +2519,13 @@
         <v>75</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2591,7 +2575,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -2603,7 +2587,7 @@
         <v>75</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>75</v>
@@ -2614,13 +2598,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="B15" t="s" s="2">
         <v>112</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>75</v>
@@ -2708,24 +2692,24 @@
         <v>77</v>
       </c>
       <c r="AI15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="AJ15" t="s" s="2">
-        <v>120</v>
-      </c>
       <c r="AK15" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2748,13 +2732,13 @@
         <v>75</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2805,7 +2789,7 @@
         <v>75</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -2828,14 +2812,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -2854,16 +2838,16 @@
         <v>75</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -2901,19 +2885,19 @@
         <v>75</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -2925,7 +2909,7 @@
         <v>75</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>75</v>
@@ -2936,14 +2920,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -2962,19 +2946,19 @@
         <v>85</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>75</v>
@@ -3023,7 +3007,7 @@
         <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -3035,21 +3019,21 @@
         <v>75</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3072,17 +3056,15 @@
         <v>85</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>75</v>
@@ -3092,7 +3074,7 @@
         <v>75</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="T19" t="s" s="2">
         <v>75</v>
@@ -3131,7 +3113,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>84</v>
@@ -3154,10 +3136,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3180,13 +3162,13 @@
         <v>85</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3213,11 +3195,11 @@
         <v>75</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>75</v>
@@ -3235,7 +3217,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -3244,7 +3226,7 @@
         <v>84</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>96</v>
@@ -3253,15 +3235,15 @@
         <v>75</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3284,13 +3266,13 @@
         <v>75</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3341,7 +3323,7 @@
         <v>75</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -3364,14 +3346,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -3390,16 +3372,16 @@
         <v>75</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3437,19 +3419,19 @@
         <v>75</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>132</v>
+        <v>171</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>133</v>
+        <v>172</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>134</v>
+        <v>173</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -3461,7 +3443,7 @@
         <v>75</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>75</v>
@@ -3472,10 +3454,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3501,16 +3483,16 @@
         <v>98</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>75</v>
@@ -3520,7 +3502,7 @@
         <v>75</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>75</v>
@@ -3559,7 +3541,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -3574,18 +3556,18 @@
         <v>96</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3608,16 +3590,16 @@
         <v>85</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -3667,7 +3649,7 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -3682,18 +3664,18 @@
         <v>96</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3719,14 +3701,14 @@
         <v>104</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>75</v>
@@ -3775,7 +3757,7 @@
         <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -3790,18 +3772,18 @@
         <v>96</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3824,19 +3806,17 @@
         <v>85</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>75</v>
@@ -3885,7 +3865,7 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -3900,18 +3880,18 @@
         <v>96</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3934,19 +3914,19 @@
         <v>85</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="O27" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>75</v>
@@ -3995,7 +3975,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
@@ -4010,18 +3990,18 @@
         <v>96</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4044,16 +4024,16 @@
         <v>85</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4103,7 +4083,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
@@ -4112,7 +4092,7 @@
         <v>84</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>75</v>
@@ -4121,15 +4101,15 @@
         <v>75</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>159</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4155,13 +4135,13 @@
         <v>78</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4211,7 +4191,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4223,7 +4203,7 @@
         <v>75</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>75</v>
@@ -4234,13 +4214,13 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>112</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>75</v>
@@ -4328,24 +4308,24 @@
         <v>77</v>
       </c>
       <c r="AI30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="AJ30" t="s" s="2">
-        <v>120</v>
-      </c>
       <c r="AK30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4368,13 +4348,13 @@
         <v>75</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4425,7 +4405,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -4448,14 +4428,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -4474,16 +4454,16 @@
         <v>75</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -4521,19 +4501,19 @@
         <v>75</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -4545,7 +4525,7 @@
         <v>75</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>75</v>
@@ -4556,14 +4536,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -4582,19 +4562,19 @@
         <v>85</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>75</v>
@@ -4643,7 +4623,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -4655,21 +4635,21 @@
         <v>75</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4692,17 +4672,15 @@
         <v>85</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>75</v>
@@ -4712,7 +4690,7 @@
         <v>75</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>75</v>
@@ -4751,7 +4729,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>84</v>
@@ -4774,10 +4752,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4800,13 +4778,13 @@
         <v>85</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4857,7 +4835,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -4866,7 +4844,7 @@
         <v>84</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>96</v>
@@ -4875,15 +4853,15 @@
         <v>75</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4906,16 +4884,16 @@
         <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -4965,7 +4943,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -4974,7 +4952,7 @@
         <v>84</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>75</v>
@@ -4983,15 +4961,15 @@
         <v>75</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>159</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5017,13 +4995,13 @@
         <v>78</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5073,7 +5051,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5085,7 +5063,7 @@
         <v>75</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>75</v>
